--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential India Equity (FOF).xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential India Equity (FOF).xlsx
@@ -22,7 +22,7 @@
     <t>ICICI Prudential India Equity (FOF)</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -64,34 +64,40 @@
     <t>Capital Markets</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Infrastructure ETF</t>
+  </si>
+  <si>
+    <t>INF109KC16E5</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Pharma Healthcare and Diagnostics (P.H.D) Fund - Direct Plan - Growth</t>
+  </si>
+  <si>
+    <t>INF109KC1GH2</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Energy Opportunities Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109KC12W6</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Business Cycle Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109KC1P24</t>
+  </si>
+  <si>
     <t>Quantum Long Term Equity Value Fund - Direct Plan - Growth</t>
   </si>
   <si>
     <t>INF082J01036</t>
   </si>
   <si>
-    <t>ICICI Prudential Pharma Healthcare and Diagnostics (P.H.D) Fund - Direct Plan - Growth</t>
-  </si>
-  <si>
-    <t>INF109KC1GH2</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Business Cycle Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109KC1P24</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Infrastructure ETF</t>
-  </si>
-  <si>
-    <t>INF109KC16E5</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Energy Opportunities Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109KC12W6</t>
+    <t>DSP Natural Resources and New Energy Fund-Direct plan-Growth</t>
+  </si>
+  <si>
+    <t>INF740K01QA7</t>
   </si>
   <si>
     <t>ICICI Prudential Dividend Yield Equity Fund Direct - Growth</t>
@@ -112,42 +118,36 @@
     <t>INF109K01Z48</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty FMCG ETF</t>
+  </si>
+  <si>
+    <t>INF109KC19V3</t>
+  </si>
+  <si>
     <t>Nippon India ETF Nifty Bank</t>
   </si>
   <si>
     <t>INF204KB15I9</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Bank ETF</t>
+  </si>
+  <si>
+    <t>INF109KC15I8</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Focused Equity Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109K018N2</t>
+  </si>
+  <si>
     <t>PGIM India Large Cap Fund - Direct - Growth</t>
   </si>
   <si>
     <t>INF663L01GR4</t>
   </si>
   <si>
-    <t>ICICI Prudential Nifty Bank ETF</t>
-  </si>
-  <si>
-    <t>INF109KC15I8</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Focused Equity Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109K018N2</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty FMCG ETF</t>
-  </si>
-  <si>
-    <t>INF109KC19V3</t>
-  </si>
-  <si>
-    <t>DSP Natural Resources and New Energy Fund-Direct plan-Growth</t>
-  </si>
-  <si>
-    <t>INF740K01QA7</t>
-  </si>
-  <si>
     <t>Reliance CPSE ETF</t>
   </si>
   <si>
@@ -169,7 +169,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -181,7 +181,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - BSE 500 TRI 1</t>
+    <t>Benchmark name - S&amp;P BSE 500 TRI</t>
   </si>
 </sst>
 </file>
@@ -975,10 +975,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="9">
-        <v>14688.88</v>
+        <v>17314.93</v>
       </c>
       <c r="G5" s="10">
-        <v>0.9617819541058</v>
+        <v>0.9692772152326</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>12</v>
@@ -998,13 +998,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="14">
-        <v>1724236.043</v>
+        <v>2172486.269</v>
       </c>
       <c r="F6" s="15">
-        <v>1507.58</v>
+        <v>1950.55</v>
       </c>
       <c r="G6" s="16">
-        <v>0.0987116266435</v>
+        <v>0.1091903734045</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>12</v>
@@ -1024,13 +1024,13 @@
         <v>15</v>
       </c>
       <c r="E7" s="14">
-        <v>1010810.031</v>
+        <v>1799200</v>
       </c>
       <c r="F7" s="15">
-        <v>1273.62</v>
+        <v>1651.49</v>
       </c>
       <c r="G7" s="16">
-        <v>0.0833926570568</v>
+        <v>0.0924492116448</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>12</v>
@@ -1050,13 +1050,13 @@
         <v>15</v>
       </c>
       <c r="E8" s="14">
-        <v>3179290.003</v>
+        <v>3574318.974</v>
       </c>
       <c r="F8" s="15">
-        <v>1266.95</v>
+        <v>1482.27</v>
       </c>
       <c r="G8" s="16">
-        <v>0.0829559263031</v>
+        <v>0.0829763988548</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>12</v>
@@ -1076,13 +1076,13 @@
         <v>15</v>
       </c>
       <c r="E9" s="14">
-        <v>5301338.999</v>
+        <v>13339014.831</v>
       </c>
       <c r="F9" s="15">
-        <v>1224.08</v>
+        <v>1353.91</v>
       </c>
       <c r="G9" s="16">
-        <v>0.080148932688</v>
+        <v>0.075790899211</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>12</v>
@@ -1102,13 +1102,13 @@
         <v>15</v>
       </c>
       <c r="E10" s="14">
-        <v>1374200</v>
+        <v>5301338.999</v>
       </c>
       <c r="F10" s="15">
-        <v>1182.64</v>
+        <v>1332.23</v>
       </c>
       <c r="G10" s="16">
-        <v>0.0774355710036</v>
+        <v>0.0745772685451</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>12</v>
@@ -1128,13 +1128,13 @@
         <v>15</v>
       </c>
       <c r="E11" s="14">
-        <v>11645977.79</v>
+        <v>1010810.031</v>
       </c>
       <c r="F11" s="15">
-        <v>1088.90</v>
+        <v>1315.06</v>
       </c>
       <c r="G11" s="16">
-        <v>0.0712977687765</v>
+        <v>0.0736161044061</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>12</v>
@@ -1154,13 +1154,13 @@
         <v>15</v>
       </c>
       <c r="E12" s="14">
-        <v>1722218.755</v>
+        <v>1308797.231</v>
       </c>
       <c r="F12" s="15">
-        <v>931.38</v>
+        <v>1276.98</v>
       </c>
       <c r="G12" s="16">
-        <v>0.060983851486</v>
+        <v>0.0714844136423</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>12</v>
@@ -1180,13 +1180,13 @@
         <v>15</v>
       </c>
       <c r="E13" s="14">
-        <v>469097.996</v>
+        <v>1722218.755</v>
       </c>
       <c r="F13" s="15">
-        <v>904.83</v>
+        <v>983.73</v>
       </c>
       <c r="G13" s="16">
-        <v>0.0592454404647</v>
+        <v>0.0550684914661</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>12</v>
@@ -1206,13 +1206,13 @@
         <v>15</v>
       </c>
       <c r="E14" s="14">
-        <v>341310.473</v>
+        <v>469097.996</v>
       </c>
       <c r="F14" s="15">
-        <v>793.31</v>
+        <v>954.37</v>
       </c>
       <c r="G14" s="16">
-        <v>0.0519434594068</v>
+        <v>0.0534249399739</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>12</v>
@@ -1232,13 +1232,13 @@
         <v>15</v>
       </c>
       <c r="E15" s="14">
-        <v>139700</v>
+        <v>410626.292</v>
       </c>
       <c r="F15" s="15">
-        <v>710.21</v>
+        <v>899.35</v>
       </c>
       <c r="G15" s="16">
-        <v>0.0465023311257</v>
+        <v>0.0503449603042</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>12</v>
@@ -1258,13 +1258,13 @@
         <v>15</v>
       </c>
       <c r="E16" s="14">
-        <v>181974.828</v>
+        <v>1512045</v>
       </c>
       <c r="F16" s="15">
-        <v>681.13</v>
+        <v>890.14</v>
       </c>
       <c r="G16" s="16">
-        <v>0.0445982636117</v>
+        <v>0.0498293911882</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>12</v>
@@ -1284,13 +1284,13 @@
         <v>15</v>
       </c>
       <c r="E17" s="14">
-        <v>1347889</v>
+        <v>139700</v>
       </c>
       <c r="F17" s="15">
-        <v>679.20</v>
+        <v>799.22</v>
       </c>
       <c r="G17" s="16">
-        <v>0.0444718932436</v>
+        <v>0.0447397555727</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>12</v>
@@ -1310,13 +1310,13 @@
         <v>15</v>
       </c>
       <c r="E18" s="14">
-        <v>718402.346</v>
+        <v>1347889</v>
       </c>
       <c r="F18" s="15">
-        <v>673.36</v>
+        <v>763.31</v>
       </c>
       <c r="G18" s="16">
-        <v>0.0440895082958</v>
+        <v>0.0427295398341</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>12</v>
@@ -1336,13 +1336,13 @@
         <v>15</v>
       </c>
       <c r="E19" s="14">
-        <v>1130045</v>
+        <v>718402.346</v>
       </c>
       <c r="F19" s="15">
-        <v>671.47</v>
+        <v>736.65</v>
       </c>
       <c r="G19" s="16">
-        <v>0.0439657570028</v>
+        <v>0.0412371323823</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>12</v>
@@ -1362,13 +1362,13 @@
         <v>15</v>
       </c>
       <c r="E20" s="14">
-        <v>682453.438</v>
+        <v>181974.828</v>
       </c>
       <c r="F20" s="15">
-        <v>626.49</v>
+        <v>719.91</v>
       </c>
       <c r="G20" s="16">
-        <v>0.0410206071823</v>
+        <v>0.0403000393312</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>12</v>
@@ -1388,13 +1388,13 @@
         <v>15</v>
       </c>
       <c r="E21" s="14">
-        <v>547726</v>
+        <v>224726</v>
       </c>
       <c r="F21" s="15">
-        <v>473.73</v>
+        <v>205.76</v>
       </c>
       <c r="G21" s="16">
-        <v>0.0310183598149</v>
+        <v>0.0115182954713</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>12</v>
@@ -1425,10 +1425,10 @@
         <v>12</v>
       </c>
       <c r="F23" s="9">
-        <v>669.39</v>
+        <v>601.49</v>
       </c>
       <c r="G23" s="10">
-        <v>0.0438295651036</v>
+        <v>0.0336709736736</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>12</v>
@@ -1459,10 +1459,10 @@
         <v>12</v>
       </c>
       <c r="F25" s="18">
-        <v>-85.70230699999775</v>
+        <v>-52.665722199999436</v>
       </c>
       <c r="G25" s="19">
-        <v>-0.005611519210307929</v>
+        <v>-0.0029481889070456613</v>
       </c>
       <c r="H25" s="18" t="s">
         <v>12</v>
@@ -1485,10 +1485,10 @@
         <v>12</v>
       </c>
       <c r="F26" s="18">
-        <v>15272.567693</v>
+        <v>17863.7542778</v>
       </c>
       <c r="G26" s="19">
-        <v>0.9999999999990924</v>
+        <v>0.9999999999991542</v>
       </c>
       <c r="H26" s="18" t="s">
         <v>12</v>
